--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B70DC8-1289-444C-8AD1-42748A185F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6CD503-912D-1541-AF09-7EFE029D04B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="5640" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="6640" yWindow="2620" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="197">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -619,6 +619,15 @@
   <si>
     <t>IFK Göteborg</t>
   </si>
+  <si>
+    <t>11.07.2026</t>
+  </si>
+  <si>
+    <t>Mjällby AIF</t>
+  </si>
+  <si>
+    <t>Matchday 12</t>
+  </si>
 </sst>
 </file>
 
@@ -989,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK16"/>
+  <dimension ref="A1:RK17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4258,7 +4267,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G16" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G17" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -20946,6 +20955,45 @@
       </c>
       <c r="L16">
         <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" t="s">
+        <v>195</v>
+      </c>
+      <c r="E17">
+        <v>3.15</v>
+      </c>
+      <c r="F17">
+        <v>1.35</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>-1.7999999999999998</v>
+      </c>
+      <c r="H17">
+        <v>63</v>
+      </c>
+      <c r="I17">
+        <v>335</v>
+      </c>
+      <c r="J17">
+        <v>157</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6CD503-912D-1541-AF09-7EFE029D04B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8B8DE3-5FB8-674A-94DF-8747EFCB6CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6640" yWindow="2620" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="2900" yWindow="2700" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="200">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -628,6 +628,15 @@
   <si>
     <t>Matchday 12</t>
   </si>
+  <si>
+    <t>Matchday 13</t>
+  </si>
+  <si>
+    <t>AIK Solna (H) 2:0</t>
+  </si>
+  <si>
+    <t>18.07.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -998,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK17"/>
+  <dimension ref="A1:RK18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4267,7 +4276,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G17" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G18" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -20993,6 +21002,45 @@
         <v>10</v>
       </c>
       <c r="L17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>0.86</v>
+      </c>
+      <c r="F18">
+        <v>1.31</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>0.45000000000000007</v>
+      </c>
+      <c r="H18">
+        <v>67</v>
+      </c>
+      <c r="I18">
+        <v>355</v>
+      </c>
+      <c r="J18">
+        <v>141</v>
+      </c>
+      <c r="K18">
+        <v>6</v>
+      </c>
+      <c r="L18">
         <v>14</v>
       </c>
     </row>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8B8DE3-5FB8-674A-94DF-8747EFCB6CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8134BE7-7B68-B744-A7F1-268EB97EB01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2900" yWindow="2700" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="6000" yWindow="-19420" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="203">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -637,6 +637,15 @@
   <si>
     <t>18.07.2026</t>
   </si>
+  <si>
+    <t>Matchday 14</t>
+  </si>
+  <si>
+    <t>AIK Solna (A) 0:0</t>
+  </si>
+  <si>
+    <t>27.07.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -1007,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK18"/>
+  <dimension ref="A1:RK19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4276,7 +4285,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G18" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G19" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21042,6 +21051,45 @@
       </c>
       <c r="L18">
         <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19">
+        <v>2.17</v>
+      </c>
+      <c r="F19">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>-1.6</v>
+      </c>
+      <c r="H19">
+        <v>24</v>
+      </c>
+      <c r="I19">
+        <v>283</v>
+      </c>
+      <c r="J19">
+        <v>128</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8134BE7-7B68-B744-A7F1-268EB97EB01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708ED518-E9CA-6E4D-89AE-49E446A2E798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="-19420" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="1420" yWindow="4200" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="206">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -646,6 +646,15 @@
   <si>
     <t>27.07.2026</t>
   </si>
+  <si>
+    <t>Matchday 15</t>
+  </si>
+  <si>
+    <t>02.08.2026</t>
+  </si>
+  <si>
+    <t>Örgryte IS</t>
+  </si>
 </sst>
 </file>
 
@@ -680,8 +689,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1016,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK19"/>
+  <dimension ref="A1:RK20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4285,7 +4295,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G19" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G20" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21090,6 +21100,45 @@
       </c>
       <c r="L19">
         <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>203</v>
+      </c>
+      <c r="B20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" t="s">
+        <v>205</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>1.47</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>-0.53</v>
+      </c>
+      <c r="H20">
+        <v>30</v>
+      </c>
+      <c r="I20">
+        <v>349</v>
+      </c>
+      <c r="J20">
+        <v>145</v>
+      </c>
+      <c r="K20">
+        <v>12</v>
+      </c>
+      <c r="L20">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708ED518-E9CA-6E4D-89AE-49E446A2E798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9701E2-E5B5-FC4F-BB14-307131055D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="4200" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="1740" yWindow="2620" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="209">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -655,6 +655,15 @@
   <si>
     <t>Örgryte IS</t>
   </si>
+  <si>
+    <t>Matchday 16</t>
+  </si>
+  <si>
+    <t>AIK Solna (A) 3:4</t>
+  </si>
+  <si>
+    <t>08.08.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -1026,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK20"/>
+  <dimension ref="A1:RK21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4295,7 +4304,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G20" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G21" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21139,6 +21148,45 @@
       </c>
       <c r="L20">
         <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C21" t="s">
+        <v>208</v>
+      </c>
+      <c r="D21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E21">
+        <v>1.98</v>
+      </c>
+      <c r="F21">
+        <v>2.83</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="H21">
+        <v>67</v>
+      </c>
+      <c r="I21">
+        <v>414</v>
+      </c>
+      <c r="J21">
+        <v>115</v>
+      </c>
+      <c r="K21">
+        <v>12</v>
+      </c>
+      <c r="L21">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9701E2-E5B5-FC4F-BB14-307131055D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB59302C-4ED6-9F47-AC95-767242C1FBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="2620" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="4900" yWindow="-17000" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="212">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -664,6 +664,15 @@
   <si>
     <t>08.08.2026</t>
   </si>
+  <si>
+    <t>Matchday 17</t>
+  </si>
+  <si>
+    <t>AIK Solna (A) 1:3</t>
+  </si>
+  <si>
+    <t>16.08.2026</t>
+  </si>
 </sst>
 </file>
 
@@ -1035,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK21"/>
+  <dimension ref="A1:RK22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4304,7 +4313,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G21" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G22" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21187,6 +21196,45 @@
       </c>
       <c r="L21">
         <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>209</v>
+      </c>
+      <c r="B22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" t="s">
+        <v>211</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="F22">
+        <v>1.74</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>-0.32999999999999985</v>
+      </c>
+      <c r="H22">
+        <v>65</v>
+      </c>
+      <c r="I22">
+        <v>342</v>
+      </c>
+      <c r="J22">
+        <v>170</v>
+      </c>
+      <c r="K22">
+        <v>12</v>
+      </c>
+      <c r="L22">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
